--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487708_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487708_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.014</v>
+        <v>5.1652</v>
       </c>
       <c r="E2" t="n">
-        <v>3.781</v>
+        <v>3.341</v>
       </c>
       <c r="F2" t="n">
-        <v>2.233</v>
+        <v>1.8242</v>
       </c>
       <c r="G2" t="n">
         <v>1.2426</v>
@@ -610,13 +610,13 @@
         <v>2.3284</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2191</v>
+        <v>0.3704</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1839</v>
+        <v>-0.256</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0352</v>
+        <v>0.6264</v>
       </c>
       <c r="V2" t="n">
         <v>1.2239</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ CAÑAS</t>
+          <t>G. DIAZ MONTERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2722</v>
+        <v>4.4195</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8507</v>
+        <v>3.0595</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4215</v>
+        <v>1.36</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3105</v>
+        <v>4.4497</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5629</v>
+        <v>2.872</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.2524</v>
+        <v>1.5777</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8872</v>
+        <v>4.568</v>
       </c>
       <c r="K3" t="n">
-        <v>2.311</v>
+        <v>3.2461</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.4237</v>
+        <v>1.3219</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5767</v>
+        <v>-0.1183</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7481</v>
+        <v>-0.374</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8286</v>
+        <v>0.2558</v>
       </c>
       <c r="P3" t="n">
-        <v>2.7164</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7164</v>
+        <v>1.3582</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3513</v>
+        <v>-0.0123</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1066</v>
+        <v>-0.1324</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4579</v>
+        <v>0.12</v>
       </c>
       <c r="V3" t="n">
-        <v>0.894</v>
+        <v>0.5642</v>
       </c>
       <c r="W3" t="n">
-        <v>2.0701</v>
+        <v>0.5642</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.1761</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. DIAZ MONTERO</t>
+          <t>D. FERNANDEZ CAÑAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.91</v>
+        <v>3.4112</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6591</v>
+        <v>3.3713</v>
       </c>
       <c r="F4" t="n">
-        <v>1.251</v>
+        <v>0.0399</v>
       </c>
       <c r="G4" t="n">
-        <v>4.4497</v>
+        <v>0.3105</v>
       </c>
       <c r="H4" t="n">
-        <v>2.872</v>
+        <v>1.5629</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5777</v>
+        <v>-1.2524</v>
       </c>
       <c r="J4" t="n">
-        <v>4.568</v>
+        <v>1.8872</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2461</v>
+        <v>2.311</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3219</v>
+        <v>-0.4237</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1183</v>
+        <v>-1.5767</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.374</v>
+        <v>-0.7481</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2558</v>
+        <v>-0.8286</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5821</v>
+        <v>2.7164</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3582</v>
+        <v>2.7164</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5218</v>
+        <v>-0.5097</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.5861</v>
       </c>
       <c r="U4" t="n">
-        <v>0.011</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5642</v>
+        <v>0.894</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5642</v>
+        <v>2.0701</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.1761</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5866</v>
+        <v>2.1767</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1416</v>
+        <v>2.541</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.555</v>
+        <v>-0.3643</v>
       </c>
       <c r="G5" t="n">
         <v>1.5195</v>
@@ -844,13 +844,13 @@
         <v>1.5523</v>
       </c>
       <c r="S5" t="n">
-        <v>0.079</v>
+        <v>-0.3309</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5473</v>
+        <v>-0.0533</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4683</v>
+        <v>-0.2776</v>
       </c>
       <c r="V5" t="n">
         <v>-0.5642</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1992</v>
+        <v>1.8966</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7966</v>
+        <v>1.3577</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4026</v>
+        <v>0.5389</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0076</v>
@@ -922,13 +922,13 @@
         <v>1.9403</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7335</v>
+        <v>-0.0362</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5933</v>
+        <v>-0.0323</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1402</v>
+        <v>-0.0039</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9419999999999999</v>
+        <v>1.3846</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3147</v>
+        <v>0.0462</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2567</v>
+        <v>1.3384</v>
       </c>
       <c r="G7" t="n">
         <v>0.3101</v>
@@ -1000,13 +1000,13 @@
         <v>1.7463</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4547</v>
+        <v>-0.0121</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4116</v>
+        <v>-0.0508</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0431</v>
+        <v>0.0387</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6597</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ LARRE</t>
+          <t>J. ATIENZA PEREA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4086</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2874</v>
+        <v>-0.4382</v>
       </c>
       <c r="F8" t="n">
-        <v>1.696</v>
+        <v>1.2513</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6186</v>
+        <v>-1.5209</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7911</v>
+        <v>-2.5581</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1725</v>
+        <v>1.0372</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3</v>
+        <v>0.2276</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.2111</v>
+        <v>-1.6271</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.08890000000000001</v>
+        <v>1.8547</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3187</v>
+        <v>-1.7485</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.58</v>
+        <v>-0.931</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2614</v>
+        <v>-0.8175</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7761</v>
+        <v>1.7463</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7463</v>
+        <v>2.7164</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3026</v>
+        <v>-0.6362</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2412</v>
+        <v>-0.5897</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0614</v>
+        <v>-0.0465</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5537</v>
+        <v>1.2239</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2239</v>
+        <v>0.894</v>
       </c>
       <c r="X8" t="n">
         <v>0.3299</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. ATIENZA PEREA</t>
+          <t>J. DOMINGUEZ LARRE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2187</v>
+        <v>0.4325</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0599</v>
+        <v>-1.4271</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2785</v>
+        <v>1.8596</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5209</v>
+        <v>-1.6186</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.5581</v>
+        <v>-1.7911</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0372</v>
+        <v>0.1725</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2276</v>
+        <v>-1.3</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.6271</v>
+        <v>-1.2111</v>
       </c>
       <c r="L9" t="n">
-        <v>1.8547</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7485</v>
+        <v>-0.3187</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.931</v>
+        <v>-0.58</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8175</v>
+        <v>0.2614</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7463</v>
+        <v>0.7761</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7164</v>
+        <v>1.7463</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2306</v>
+        <v>-0.2787</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2113</v>
+        <v>-0.3808</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0193</v>
+        <v>0.1021</v>
       </c>
       <c r="V9" t="n">
+        <v>1.5537</v>
+      </c>
+      <c r="W9" t="n">
         <v>1.2239</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.894</v>
       </c>
       <c r="X9" t="n">
         <v>0.3299</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.4001</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3743</v>
+        <v>0.5745</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2834</v>
+        <v>-0.1744</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7547</v>
@@ -1234,13 +1234,13 @@
         <v>0.5821</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.3213</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6057</v>
+        <v>-0.4055</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0249</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>0.894</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4885</v>
+        <v>-0.77</v>
       </c>
       <c r="E11" t="n">
-        <v>1.101</v>
+        <v>1.2011</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5895</v>
+        <v>-1.9711</v>
       </c>
       <c r="G11" t="n">
         <v>0.5953000000000001</v>
@@ -1312,13 +1312,13 @@
         <v>0.5821</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4136</v>
+        <v>-0.6951000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6057</v>
+        <v>-0.5056</v>
       </c>
       <c r="U11" t="n">
-        <v>0.192</v>
+        <v>-0.1895</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2821</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.754</v>
+        <v>-1.6423</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9217</v>
+        <v>-4.0008</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1677</v>
+        <v>2.3585</v>
       </c>
       <c r="G12" t="n">
         <v>-2.1133</v>
@@ -1390,13 +1390,13 @@
         <v>3.4926</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2228</v>
+        <v>-0.1111</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1795</v>
+        <v>-0.2586</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0433</v>
+        <v>0.1475</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.3762</v>
+        <v>-3.058</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.0742</v>
+        <v>-0.9741</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3019</v>
+        <v>-2.0839</v>
       </c>
       <c r="G13" t="n">
         <v>0.3701</v>
@@ -1468,13 +1468,13 @@
         <v>0.5821</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9583</v>
+        <v>-0.6401</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4722</v>
+        <v>-0.3721</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4861</v>
+        <v>-0.268</v>
       </c>
       <c r="V13" t="n">
         <v>-2.4</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14.0235</v>
+        <v>14.6291</v>
       </c>
       <c r="E14" t="n">
-        <v>8.046400000000002</v>
+        <v>8.652100000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>5.9772</v>
+        <v>5.9771</v>
       </c>
       <c r="G14" t="n">
         <v>2.7827</v>
@@ -1516,7 +1516,7 @@
         <v>3.3943</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6116</v>
+        <v>-0.6116000000000005</v>
       </c>
       <c r="J14" t="n">
         <v>14.2317</v>
@@ -1525,7 +1525,7 @@
         <v>9.309899999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>4.921900000000001</v>
+        <v>4.9219</v>
       </c>
       <c r="M14" t="n">
         <v>-11.4493</v>
@@ -1546,13 +1546,13 @@
         <v>21.3435</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.819</v>
+        <v>-3.2133</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.228700000000001</v>
+        <v>-3.623200000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4094999999999999</v>
+        <v>0.4095999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>2.447700000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.9487</v>
+        <v>5.9469</v>
       </c>
       <c r="E15" t="n">
-        <v>6.3377</v>
+        <v>6.9383</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.389</v>
+        <v>-0.9913999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>6.4047</v>
@@ -1624,13 +1624,13 @@
         <v>1.7463</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9619</v>
+        <v>0.9601</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.005</v>
+        <v>-0.4044</v>
       </c>
       <c r="U15" t="n">
-        <v>1.9669</v>
+        <v>1.3644</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2239</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9997</v>
+        <v>1.3056</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5543</v>
+        <v>1.0538</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4454</v>
+        <v>0.2518</v>
       </c>
       <c r="G16" t="n">
         <v>-0.9446</v>
@@ -1702,13 +1702,13 @@
         <v>1.1642</v>
       </c>
       <c r="S16" t="n">
-        <v>1.904</v>
+        <v>1.2099</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8153</v>
+        <v>0.3148</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0886</v>
+        <v>0.8951</v>
       </c>
       <c r="V16" t="n">
         <v>0.8462</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1379</v>
+        <v>0.0801</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4469</v>
+        <v>0.1466</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.309</v>
+        <v>-0.0665</v>
       </c>
       <c r="G17" t="n">
         <v>-1.0196</v>
@@ -1780,13 +1780,13 @@
         <v>0.194</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3037</v>
+        <v>0.2459</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3645</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0608</v>
+        <v>0.1817</v>
       </c>
       <c r="V17" t="n">
         <v>0.6597</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0547</v>
+        <v>-0.6647</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4197</v>
+        <v>0.6189</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4743</v>
+        <v>-1.2836</v>
       </c>
       <c r="G18" t="n">
         <v>0.4688</v>
@@ -1858,13 +1858,13 @@
         <v>0.194</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1467</v>
+        <v>0.5367</v>
       </c>
       <c r="T18" t="n">
-        <v>1.2864</v>
+        <v>0.4856</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1397</v>
+        <v>0.051</v>
       </c>
       <c r="V18" t="n">
         <v>-0.894</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5977</v>
+        <v>-0.7528</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4197</v>
+        <v>-0.8201000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.178</v>
+        <v>0.0673</v>
       </c>
       <c r="G19" t="n">
         <v>-0.3364</v>
@@ -1936,13 +1936,13 @@
         <v>0.9702</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4551</v>
+        <v>0.3</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4991</v>
+        <v>0.0987</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0439</v>
+        <v>0.2014</v>
       </c>
       <c r="V19" t="n">
         <v>1.2239</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4245</v>
+        <v>-1.5425</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2311</v>
+        <v>-1.131</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1934</v>
+        <v>-0.4114</v>
       </c>
       <c r="G20" t="n">
         <v>-1.8792</v>
@@ -2014,13 +2014,13 @@
         <v>0.3881</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6308</v>
+        <v>0.5128</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0595</v>
+        <v>0.0406</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6902</v>
+        <v>0.4722</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5642</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8835</v>
+        <v>-1.5654</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1094</v>
+        <v>-1.0093</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7741</v>
+        <v>-0.5561</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2651</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0363</v>
+        <v>0.2818</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2423</v>
+        <v>-0.1422</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2059</v>
+        <v>0.424</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6119</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.0969</v>
+        <v>-3.969</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5118</v>
+        <v>-1.711</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5851</v>
+        <v>-2.2581</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6818</v>
@@ -2170,13 +2170,13 @@
         <v>1.3582</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8733</v>
+        <v>0.2546</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.3201</v>
+        <v>-0.5193</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4469</v>
+        <v>0.7739</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9896</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.6048</v>
+        <v>-5.2619</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.0675</v>
+        <v>-4.7672</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5373</v>
+        <v>-0.4947</v>
       </c>
       <c r="G23" t="n">
         <v>-1.4481</v>
@@ -2248,13 +2248,13 @@
         <v>1.7463</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2479</v>
+        <v>0.5908</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5799</v>
+        <v>-0.2796</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8278</v>
+        <v>0.8704</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3299</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.4478</v>
+        <v>-6.8871</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.3963</v>
+        <v>-5.2962</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.0515</v>
+        <v>-1.5909</v>
       </c>
       <c r="G24" t="n">
         <v>-2.0815</v>
@@ -2326,13 +2326,13 @@
         <v>0.9702</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9215</v>
+        <v>-0.3609</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1683</v>
+        <v>-0.0682</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7532</v>
+        <v>-0.2927</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5642</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-14.0236</v>
+        <v>-13.3108</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.977200000000001</v>
+        <v>-5.9772</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.0463</v>
+        <v>-7.333600000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-2.7828</v>
@@ -2404,13 +2404,13 @@
         <v>8.731499999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>3.819000000000001</v>
+        <v>4.5317</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4097999999999997</v>
+        <v>-0.4098</v>
       </c>
       <c r="U25" t="n">
-        <v>4.228700000000001</v>
+        <v>4.9414</v>
       </c>
       <c r="V25" t="n">
         <v>-2.447900000000001</v>
